--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_004/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,6 +364,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -539,11 +559,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -575,6 +590,11 @@
       </text>
     </comment>
     <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="G8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1336,17 +1356,17 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>LL-PL-SUPT-02 Feedline Support Bracket FEA</t>
+          <t>Propellant Feedline Support Bracket FEA (LL-PL-SUPT-02)</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Predict structural strength, stiffness, and thermal clamp-load retention of titanium feedline support bracket for PDR go/no-go decision</t>
+          <t>FEA of titanium feedline support bracket for random vibration, quasi-static thrust vectoring, and thermal gradient loading at PDR</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Finite-element model of Ti-6Al-4V propellant feedline support bracket (LL-PL-SUPT-02) used to demonstrate positive margin at 95th-percentile stress and first modal frequency &gt; 350 Hz under random vibration, quasi-static thrust vectoring, and -120 to +70 C thermal gradient loading conditions.</t>
+          <t>Finite-element model of Ti-6Al-4V feedline support bracket (LL-PL-SUPT-02) used to demonstrate positive strength margin at 95th-percentile stress and first modal frequency &gt; 350 Hz under combined random vibe, quasi-static thrust vectoring, and -120 to +70 C thermal gradient, as the decision basis for Preliminary Design Review.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1384,9 +1404,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (V&amp;V status memo, R. Patel, FEA Lead, 06 Aug 2026, RPT-LL-FEA-112 to -117)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1447,7 +1467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1505,7 +1525,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>STR-LL-PL-02 Bracket Structural Requirements</t>
+          <t>STR-LL-PL-02 Structural Performance Requirements</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1515,7 +1535,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Bracket must show positive margin at 95th-percentile peak stress (yield = 880 MPa) and first modal frequency &gt; 350 Hz with feedline attached, across random vibe, quasi-static thrust vectoring, and -120 to +70 C thermal gradient.</t>
+          <t>Bracket must achieve positive margin at 95th-percentile peak stress (vs. 880 MPa yield) and first modal frequency &gt; 350 Hz with feedline attached, across the full load and thermal envelope</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1537,12 +1557,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>LL-PL-SUPT-02 Abaqus FEA Model (Tag LL-PL-SUPT_R5)</t>
+          <t>Abaqus/Standard FEA Model of LL-PL-SUPT-02</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF6 linear-elastic (small-strain) FE model of Ti-6Al-4V bracket with geometric nonlinearity in preload/contact step, C3D10I tetrahedral elements, B31 bolt beams, and Coulomb contact.</t>
+          <t>Linear-elastic / contact FEA model of Ti-6Al-4V bracket using C3D10I tetrahedral elements and B31 bolt beams in Abaqus/Standard 2023 HF6, with LHS-based UQ (500 samples)</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1574,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Subscale Bracket Vibration and Strain Test Data</t>
+          <t>Subscale Bracket Test Data (STR-TST-018)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>12-gage strain measurement dataset from subscale bracket test including quasi-static load cases and modal identification (first mode 397 Hz measured); tribology coupon friction data (0.18–0.24).</t>
+          <t>Twelve-strain-gage subscale bracket test providing quasi-static strain and modal frequency data for model correlation; RMS strain error 6.1%, first mode 397 Hz measured vs. 412 Hz predicted</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1591,29 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>Material and Loads Input Data</t>
+          <t>Material and Tribology Input Data</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V AMS 4928 material properties with temperature knockdowns, quasi-static and random vibe load environments, thermal gradient node map, and NASM fastener stiffness from supplier certs.</t>
+          <t>Ti-6Al-4V AMS 4928 elastic and strength properties with temperature knockdowns; friction coefficients 0.18–0.24 from coupon tribology tests; NASM fastener stiffness from supplier certs</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Loads and Environments Data</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Quasi-static vectoring loads (±5% allocation), random vibration PSD, and thermal gradient node map used as model boundary conditions</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2050,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Strain Gage Correlation — Quasi-Static Load</t>
+          <t>Quasi-Static Strain Gage Correlation</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2028,12 +2065,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Predicted strain field compared against 12 strain gages on subscale bracket under quasi-static thrust vectoring loads</t>
+          <t>FEA-predicted surface strains compared against 12 strain gages on subscale bracket under quasi-static vectoring load</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Physical subscale bracket hardware test per STR-TST-018</t>
+          <t>Subscale bracket test data per STR-TST-018</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2070,12 +2107,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Predicted first modal frequency of bracket with attached line mass compared to experimentally identified first mode from subscale test</t>
+          <t>Predicted first modal frequency with attached line mass compared to experimentally measured first mode from subscale bracket test</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Measured first mode 397 Hz from subscale hardware test</t>
+          <t>Measured first mode 397 Hz from subscale test</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2097,7 +2134,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Micro-slip Onset Correlation</t>
+          <t>Micro-Slip Onset Correlation</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2107,12 +2144,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Predicted onset of micro-slip at bolt pads compared to experimentally observed onset in subscale test</t>
+          <t>Predicted load at onset of micro-slip in contact interface compared to test observation</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Experimental micro-slip onset from subscale bracket test</t>
+          <t>Subscale bracket test observation</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2144,12 +2181,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Three-mesh refinement study (1.2M, 3.5M, 6.4M elements) on peak von Mises stress and first modal frequency using Richardson extrapolation</t>
+          <t>Three-mesh Richardson extrapolation study on peak von Mises stress at inner fillet and first modal frequencies; 1.2M, 3.5M, and 6.4M element meshes</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation asymptotic value (655 MPa)</t>
+          <t>Richardson-extrapolated asymptotic value (655 MPa)</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2159,12 +2196,12 @@
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation</t>
+          <t>Richardson extrapolation / Grid Convergence Index</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Finest mesh 648 MPa; numerical shortfall ~4.1%; modal frequency change &lt; 1.8% between two finest meshes</t>
+          <t>Finest-mesh value 648 MPa; numerical shortfall ~4.1%; modal frequency change &lt; 1.8% between last two meshes</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2176,7 +2213,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>UQ Latin-Hypercube Propagation — 95th Percentile Margin</t>
+          <t>NAFEMS Benchmark Verification</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2186,27 +2223,22 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>500 Latin-hypercube samples propagating E, friction, pretension, and load scatter through mid-mesh model to establish 95th-percentile peak stress and 5th-percentile first mode</t>
+          <t>Code verification against NAFEMS LE10 (linear elastic stress) and VB08 (contact patch pressure) benchmark problems</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Requirements: P95 stress &lt; 880 MPa yield; P5 frequency &gt; 350 Hz</t>
+          <t>NAFEMS reference solutions</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Latin Hypercube Sampling, Sobol sensitivity indices</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>P95 peak stress 702 MPa, margin = 0.25; P5 frequency 386 Hz &gt; 350 Hz target</t>
+          <t>Errors &lt; 1.2% for linear elastic stress; &lt; 3.5% for contact patch pressure</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2218,7 +2250,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>NAFEMS Benchmark Verification (LE10 and VB08)</t>
+          <t>UQ / Probabilistic Margin Assessment</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -2228,22 +2260,27 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Abaqus solver benchmarked against NAFEMS LE10 linear elastic stress problem and VB08 vibration benchmark to verify numerical accuracy</t>
+          <t>500 Latin-hypercube samples propagating uncertainty in E, friction, pretension, and load scatter through mid-mesh model to establish 95th-percentile stress and 5th-percentile frequency</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>NAFEMS benchmark reference solutions</t>
+          <t>Requirements: P95 stress vs. 880 MPa yield; P5 frequency vs. 350 Hz target</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Latin Hypercube Sampling; Sobol sensitivity indices</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Linear elastic stress error &lt; 1.2%; contact patch pressure error &lt; 3.5%</t>
+          <t>P95 peak stress 702 MPa; margin = 0.25; P5 first mode 386 Hz &gt; 350 Hz</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -2397,12 +2434,12 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Solver is verified commercial code with documented benchmark results and script-level unit testing</t>
+          <t>Simulation software is verified via established benchmarks and configuration-controlled</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF6 used as commercial solver. Benchmarked against NAFEMS LE10 (&lt;1.2% error) and VB08 (&lt;3.5% contact pressure error). Custom bolt-preload Python utilities have 13 unit tests passing with energy balance verification on a lap joint. Models and scripts under Git LFS version control (tag LL-PL-SUPT_R5); job files archived to Windchill with checksums. Prior workflow applied to LL-AVIO-27 with demonstrated test correlation within 5% static and 4% modal.</t>
+          <t>Abaqus/Standard 2023 HF6 (commercial solver) benchmarked against NAFEMS LE10 and VB08 with errors &lt; 1.2% and &lt; 3.5% respectively. Custom Python bolt-preload utilities have 13 unit test cases passing and an energy balance check. All model files and scripts are under Git LFS version control (tag LL-PL-SUPT_R5) with Windchill archival and checksums. Prior workflow validated on LL-AVIO-27 with ETU and flight data.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2431,12 +2468,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code correctly solves governing equations as demonstrated by comparison to analytical or benchmark solutions</t>
+          <t>Code correctly solves governing equations as demonstrated by benchmark comparison</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Abaqus solver verified against NAFEMS LE10 (linear elastic stress, error &lt;1.2%) and VB08 (vibration benchmark, error &lt;3.5% contact patch pressure). These are established benchmark problems for structural FEA. Custom script unit tests (13 cases) provide additional verification of preprocessing utilities.</t>
+          <t>NAFEMS LE10 benchmark (linear elastic stress) error &lt; 1.2%; NAFEMS VB08 benchmark (contact patch pressure) error &lt; 3.5%. Custom preload scripts verified with 13 unit tests and lap-joint energy balance. These are recognized benchmark problems for structural FEA code verification.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2465,12 +2502,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh refinement study demonstrates convergence of peak stress and modal frequency QoIs</t>
+          <t>Mesh convergence demonstrated with quantified numerical error at the critical location</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three meshes studied: 1.2M, 3.5M, and 6.4M elements. Richardson extrapolation applied to peak von Mises stress, yielding asymptotic value of 655 MPa; finest mesh (648 MPa) gives estimated numerical shortfall of ~4.1%. First modal frequency changed &lt;1.8% between the two finest meshes. Local refinement to 0.6 mm at bolt pads. Open item: hexahedral-dominant spot-check mesh at hot spot planned (ETA 1 week).</t>
+          <t>Three-mesh convergence study (1.2M, 3.5M, 6.4M elements). Richardson extrapolation yields asymptotic peak von Mises of 655 MPa; finest mesh gives 648 MPa, numerical shortfall ~4.1%. Modal frequencies converged to within 1.8% between the two finest meshes. Local refinement to 0.6 mm at bolt pads. Open item: hex-dominant spot check at hot spot planned (ETA 1 week).</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2492,19 +2529,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Solver convergence confirmed with tightened tolerances; no pathological contact behavior observed</t>
+          <t>Iterative convergence adequately controlled and monitored</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Force residual convergence tolerance tightened to 5e-4. Automatic stabilization disabled. NLGEOM on during preload/contact step, off for linear dynamics. No cutbacks or contact chatter observed in final mesh runs. Sensitivity to contact enforcement method (penalty vs. kinematic) shifts peak stress by &lt;2.5%, confirming solver robustness.</t>
+          <t>Force residual tolerance tightened to 5e-4; NLGEOM applied selectively (on during preload/contact step, off for linear dynamics). Automatic stabilization disabled. No cutbacks or contact chatter observed in final mesh runs. Solver increment sensitivity check: changing penalty vs. kinematic contact enforcement moved peak stress &lt; 2.5%.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2533,12 +2570,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review confirms correct model setup including boundary conditions, loads, and mesh quality</t>
+          <t>Model set-up independently reviewed and verified for correctness</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Peer review held 02 Aug 2026; red team identified missing pretension scatter in early runs — subsequently addressed. Independent structures panel concurrence granted 05 Aug 2026 with two minor actions closed. Boundary conditions verified against test stand per STR-TST-018. Full parameter map links each figure to exact job ID. Run summaries RPT-LL-FEA-112 to -117 include meshes, solver settings, and seed values with postprocessing notebooks embedding metadata.</t>
+          <t>Independent peer review held 02 Aug 2026; red-team identified missing pretension scatter in early runs — subsequently addressed. Independent structures panel concurrence given 05 Aug with two minor actions closed. Fixture boundary conditions verified to match test stand per STR-TST-018. All inputs traced to controlled sources in DOORS module STR-LL-PL-02. Parameter map links every figure to exact job ID for traceability. Team includes PE with 12 years experience.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2567,12 +2604,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and physics scope choices are justified with known limitations documented</t>
+          <t>Governing equations and modeling choices justified and limitations documented</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Small-strain linear elasticity chosen for Ti-6Al-4V; geometric nonlinearity enabled only in preload/contact step. Model scope explicitly excludes fatigue, crack growth, adhesive effects, large plasticity, wear, and fretting — documented as out of scope for this phase with separate CDR analyses planned. Physics choices are appropriate for PDR-level linear stress and modal assessment. No adhesive modeled; dry-contact Coulomb friction used.</t>
+          <t>Small-strain linear elasticity selected for Ti-6Al-4V as justified for the stress regime; geometric nonlinearity enabled only in preload/contact step as appropriate. Known out-of-scope physics (fatigue, crack growth, adhesive effects, large plasticity, wear, fretting) explicitly identified. Applicability domain stated: -130 to +90 C, pretension 7–10 kN, friction 0.18–0.24, loads within Rev C/G envelopes. Dry-contact with Coulomb friction modeled. Separate analyses planned for CDR. Model form not independently validated beyond the subscale correlation.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2601,12 +2638,12 @@
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Material properties, loads, and boundary conditions are traceable to controlled sources with uncertainty characterization</t>
+          <t>Material properties, loads, and boundary conditions are traceable to controlled, measured sources with uncertainty characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V properties from MMPDS-17 (AMS 4928): E=114±3% GPa, yield=880 MPa with temperature knockdowns per LL-MP-221. Friction 0.18–0.24 from coupon tribology TN-TRIB-042. Pretension 8.5±0.8 kN from torque-preload curve. Loads from GN&amp;C Rev C (±5% allocation), PSD from Environments Rev G, thermal gradient from TMM Rev C. NASM fastener stiffness from supplier certs. No backfitting performed; all inputs traceable to DOORS STR-LL-PL-02. Open item: updated friction CDFs from second tribology batch pending (ETA 2 weeks).</t>
+          <t>Ti-6Al-4V AMS 4928 properties from MMPDS-17 (E=114±3% GPa); temperature knockdowns from M&amp;P memo LL-MP-221. Friction 0.18–0.24 from coupon tribology TN-TRIB-042. NASM fastener stiffness from supplier certs. Pretension 8.5±0.8 kN from torque-preload curve. Loads from GN&amp;C Rev C (±5% allocation) and Environments Rev G. Thermal gradient from TMM Rev C with node map. No backfitting performed. Uncertainty bounds explicitly quantified for all major inputs and propagated in UQ study. Open item: updated friction CDFs from second tribology batch pending (ETA 2 weeks).</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2635,12 +2672,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test articles are described and representative of flight configuration</t>
+          <t>Test articles are adequately described and representative of the design</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Subscale bracket test specimen with attached mass used; 12 strain gages installed. The memo describes it as a subscale article (not full-scale flight-representative hardware). Number of specimens tested not explicitly stated — likely a single test article. No statistical characterization of sample population or production-representativeness documented beyond the single subscale test.</t>
+          <t>Subscale bracket with attached mass used for correlation; 12 strain gages instrumented. The memo describes this as a subscale (not full-scale) test article. Only one test configuration is referenced. No mention of multiple specimens, statistical characterization of hardware variability, or production-representative sample size justification. The subscale nature is a gap relative to the as-designed geometry.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2662,19 +2699,19 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions are controlled and calibrated with documented measurement uncertainty</t>
+          <t>Test conditions are controlled and measured with documented uncertainty</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Test conducted per STR-TST-018 which defines fixture boundary conditions mimicking the test stand. 12 strain gages used for quasi-static load correlation; modal identification performed. Friction coupon tests documented in TN-TRIB-042. Explicit calibration records and instrument measurement uncertainty values are not reported in this memo, but test was conducted against a controlled procedure.</t>
+          <t>Fixture boundary conditions documented per STR-TST-018 and verified to mimic test stand. Quasi-static vectoring loads applied with defined allocation. Strain gage placement and measurement referenced. However, the memo does not explicitly state instrument calibration records, environmental control details, or formal measurement uncertainty quantification for the test data itself. Adequate evidence for PDR-level correlation.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2703,12 +2740,12 @@
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions and input parameters demonstrably match test conditions</t>
+          <t>Model inputs demonstrably match experimental test conditions</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Fixture boundary condition explicitly set to mimic test stand per STR-TST-018. Feedline represented as beam with equivalent bending and inertia from system team. Pretension set to torque-preload curve matching hardware assembly. Friction range retained as tested (0.18–0.24) without adjustment. Thermal gradient from TMM Rev C with node map provided. No explicit uncertainty propagation from test measurement uncertainty to input parameters is documented, but parameter sources are all traceable.</t>
+          <t>Fixture BC in model mimics test stand per STR-TST-018. Friction range, pretension, and loads as-tested are used in the model without backfitting. Pretension set to 8.5±0.8 kN per torque-preload curve consistent with test configuration. Subscale geometry differences are acknowledged but not fully quantified in terms of input equivalency. No explicit propagation of test measurement uncertainty into model input matching.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2733,16 +2770,16 @@
         <v>3</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison between model predictions and test measurements across multiple output quantities</t>
+          <t>Quantitative comparison between model predictions and test data with error metrics</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Multiple QoIs compared: (1) strain field — RMS error 6.1% across 12 gages, worst-case 9%; (2) first modal frequency — predicted 412 Hz vs. measured 397 Hz (+3.8%); (3) micro-slip onset — within 8%. UQ analysis provides 95th-percentile stress (702 MPa) and 5th-percentile frequency (386 Hz) with Sobol sensitivity decomposition (friction and pretension 66% combined, modulus 11%). Historical precedent: similar bracket LL-AVIO-27 matched ETU static tests within 5% and modal IDs within 4%.</t>
+          <t>RMS strain error 6.1% across 12 gages; worst-case gage 9%. First modal frequency: predicted 412 Hz vs. measured 397 Hz (+3.8%). Micro-slip onset within 8%. Multiple comparison points provided. UQ bands established (P95 stress, P5 frequency). However, no formal statistical validation metric (e.g., MAPE, R², u-pooled) applied; uncertainty bands on the test data itself not reported. Adequate quantitative comparison for PDR.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2771,12 +2808,12 @@
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly address the pass/fail criteria stated in the requirements and are measurable both computationally and experimentally</t>
+          <t>Model QoIs directly address the safety/performance decision requirements</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs are explicitly tied to requirements: (1) P95 von Mises stress vs. 880 MPa yield (margin = 0.25 at P95), directly addressable by FEA and measurable by strain gages; (2) first modal frequency vs. 350 Hz target, directly computed and measured via modal test (397 Hz measured, 412 Hz predicted). Micro-slip onset relevant to clamp-load retention. Sobol analysis confirms QoIs are sensitive to the dominant physical inputs.</t>
+          <t>QoIs are explicitly tied to pass/fail requirements: (1) positive margin at P95 peak von Mises stress vs. yield strength, (2) first modal frequency &gt; 350 Hz with line attached, and (3) clamp load retention across thermal gradient. These are directly measurable both computationally and experimentally (strain gages for stress proxy, accelerometer/EMA for frequency). Sobol indices additionally identify dominant contributors, supporting design decisions.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2805,12 +2842,12 @@
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation test conditions cover the intended operating envelope including temperature, load levels, and geometry</t>
+          <t>Validation conditions sufficiently cover the intended use envelope</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Subscale bracket test with attached mass covers quasi-static loading and modal characterization, directly relevant to two of three COU load cases. Model applicability stated as -130 to +90 C (encompassing COU -120 to +70 C), pretension 7–10 kN, friction 0.18–0.24, loads within Rev C/G envelopes. Gaps: thermal gradient validation not explicitly demonstrated in test; subscale (not full-scale) geometry used; random vibration regime validated indirectly through modal frequency correlation rather than direct PSD response test. Sensitivity study shows ±10% line mass keeps frequency margin adequate.</t>
+          <t>Validation performed with subscale bracket under quasi-static vectoring and modal testing, which covers the primary load cases. Physics regime (linear elastic, contact, Ti-6Al-4V) matches COU. Applicability domain stated and matches the test conditions. Gaps: (1) subscale rather than full-scale article; (2) thermal gradient loading not included in the test correlation; (3) random vibe loading not directly tested — vibe PSD envelope applied only computationally; (4) large plasticity, wear, fretting deferred to CDR. These gaps are documented and are acceptable at PDR level.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2995,7 +3032,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The LL-PL-SUPT-02 bracket FEA model is accepted as the decision basis for PDR. Validation against subscale hardware shows RMS strain error 6.1%, modal frequency error +3.8%, and micro-slip onset within 8%. UQ propagation (500 LHS samples) yields P95 stress margin of 0.25 (702 MPa vs. 880 MPa yield) and P5 first mode of 386 Hz, both satisfying requirements. Mesh convergence, solver benchmarking, independent structural panel concurrence (05 Aug 2026), and full input traceability are established. Two open items are accepted with conditions: (1) hexahedral hot-spot mesh spot check (ETA 1 week) and (2) UQ rerun with updated tribology friction CDFs (ETA 2 weeks); neither is expected to change the P95 margin trend. Applicability limits (-130 to +90 C, Rev C/G load envelopes) must be observed; fatigue, crack growth, plasticity, and fretting are out of scope pending CDR analyses.</t>
+          <t>The FEA model for LL-PL-SUPT-02 is accepted as the decision basis for PDR. Positive margin at P95 (margin=0.25) and P5 first mode of 386 Hz both satisfy requirements. Model correlation is within 9% on strain and 3.8% on frequency. Mesh convergence, UQ, independent peer review, and full input traceability are all documented. Residual gaps (hex spot-check, updated friction CDFs, absence of full-scale and thermal-gradient test correlation) are minor, acknowledged, time-bounded, and appropriate to defer to CDR. The model must not be used outside the stated applicability limits (-130 to +90 C, pretension 7–10 kN, friction 0.18–0.24, loads within Rev C/G envelopes), and the open UQ rerun with updated friction CDFs must be completed before CDR.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3005,7 +3042,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>R. Patel (FEA Lead); Independent Structures Panel</t>
+          <t>R. Patel (FEA Lead); Independent Structures Panel concurrence 05 Aug 2026</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
